--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1884.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1884.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E6E016-9B5F-4789-B597-B5F34DF5CBFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{E49FF23B-5D0B-4DAE-84F9-7D6D171212C5}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{E49FF23B-5D0B-4DAE-84F9-7D6D171212C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1884.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1884.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E6E016-9B5F-4789-B597-B5F34DF5CBFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A51131-4A82-498E-BD50-D51DA1E0EB31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{E49FF23B-5D0B-4DAE-84F9-7D6D171212C5}"/>
   </bookViews>
@@ -48,9 +48,6 @@
     <t>чр YY</t>
   </si>
   <si>
-    <t>чс YY</t>
-  </si>
-  <si>
     <t>р YY</t>
   </si>
   <si>
@@ -412,6 +409,9 @@
   </si>
   <si>
     <t>ошибочны и следует использовать величины ЦСК</t>
+  </si>
+  <si>
+    <t>чу YY</t>
   </si>
 </sst>
 </file>
@@ -842,82 +842,82 @@
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -950,52 +950,52 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N1" s="4"/>
       <c r="O1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="5">
         <v>327442</v>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="5">
         <v>793052</v>
@@ -1067,7 +1067,7 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="5">
         <v>1424115</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="5">
         <v>956137</v>
@@ -1139,7 +1139,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B7" s="5">
         <v>406365</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="5">
         <v>1238041</v>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="5">
         <v>1204951</v>
@@ -1247,7 +1247,7 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="5">
         <v>1358785</v>
@@ -1283,7 +1283,7 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="5">
         <v>1199577</v>
@@ -1319,7 +1319,7 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="5">
         <v>2140490</v>
@@ -1355,7 +1355,7 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="5">
         <v>2486195</v>
@@ -1391,7 +1391,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" s="5">
         <v>2839206</v>
@@ -1427,7 +1427,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="5">
         <v>1243414</v>
@@ -1463,7 +1463,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16" s="5">
         <v>1664715</v>
@@ -1499,7 +1499,7 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B17" s="5">
         <v>439149</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18" s="5">
         <v>404700</v>
@@ -1571,7 +1571,7 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" s="5">
         <v>2040448</v>
@@ -1607,7 +1607,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B20" s="5">
         <v>794414</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B21" s="5">
         <v>1156617</v>
@@ -1679,7 +1679,7 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="5">
         <v>2554826</v>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23" s="5">
         <v>1482858</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="5">
         <v>1308417</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B25" s="5">
         <v>656496</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B26" s="5">
         <v>2362988</v>
@@ -1859,7 +1859,7 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5">
         <v>654377</v>
@@ -1895,7 +1895,7 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5">
         <v>1198058</v>
@@ -1931,7 +1931,7 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5">
         <v>575004</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5">
         <v>903662</v>
@@ -2003,7 +2003,7 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B31" s="5">
         <v>1625329</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B32" s="5">
         <v>1206311</v>
@@ -2075,7 +2075,7 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B33" s="5">
         <v>2175906</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B34" s="5">
         <v>757111</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B35" s="5">
         <v>1454790</v>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B36" s="5">
         <v>1158995</v>
@@ -2219,7 +2219,7 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B37" s="5">
         <v>330748</v>
@@ -2255,7 +2255,7 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B38" s="5">
         <v>1215886</v>
@@ -2291,7 +2291,7 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B39" s="5">
         <v>1934876</v>
@@ -2327,7 +2327,7 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B40" s="5">
         <v>1434707</v>
@@ -2363,7 +2363,7 @@
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B41" s="5">
         <v>2612530</v>
@@ -2399,7 +2399,7 @@
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B42" s="5">
         <v>906914</v>
@@ -2435,7 +2435,7 @@
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B43" s="5">
         <v>565326</v>
@@ -2471,7 +2471,7 @@
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B44" s="5">
         <v>2360024</v>
@@ -2507,7 +2507,7 @@
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B45" s="5">
         <v>2617758</v>
@@ -2543,7 +2543,7 @@
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B46" s="5">
         <v>929931</v>
@@ -2579,7 +2579,7 @@
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B47" s="5">
         <v>668758</v>
@@ -2615,7 +2615,7 @@
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B48" s="5">
         <v>1760353</v>
@@ -2651,7 +2651,7 @@
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B49" s="5">
         <v>2359428</v>
@@ -2687,7 +2687,7 @@
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B50" s="5">
         <v>1619689</v>
@@ -2723,7 +2723,7 @@
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B51" s="5">
         <v>861303</v>
@@ -2760,7 +2760,7 @@
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B52" s="5">
         <v>2121336</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B53" s="5">
         <v>1503428</v>
@@ -2832,7 +2832,7 @@
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B54" s="5">
         <v>1256881</v>
@@ -2868,7 +2868,7 @@
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B55" s="5">
         <v>620043</v>
@@ -2904,7 +2904,7 @@
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B56" s="5">
         <v>641698</v>
@@ -2940,7 +2940,7 @@
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B57" s="5">
         <v>967146</v>
@@ -2976,7 +2976,7 @@
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B58" s="5">
         <v>2566447</v>
@@ -3012,7 +3012,7 @@
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B59" s="5">
         <v>1725100</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B60" s="5">
         <v>1318872</v>
@@ -3084,7 +3084,7 @@
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B61" s="5">
         <v>1163857</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B62" s="5">
         <v>1392385</v>
@@ -3156,7 +3156,7 @@
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B63" s="5">
         <v>1835630</v>
@@ -3192,7 +3192,7 @@
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B64" s="5">
         <v>2199154</v>
@@ -3228,7 +3228,7 @@
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B65" s="5">
         <v>1641892</v>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B66" s="5">
         <v>2030126</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B67" s="5">
         <v>381858</v>
@@ -3336,7 +3336,7 @@
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B68" s="5">
         <v>1086372</v>
@@ -3372,7 +3372,7 @@
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B69" s="11">
         <v>88825618</v>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B71" s="5">
         <v>463052</v>
@@ -3475,71 +3475,71 @@
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B72" s="5">
         <v>43965</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R72" s="7"/>
       <c r="S72" s="7"/>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B73" s="5">
         <v>509633</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R73" s="7"/>
       <c r="S73" s="7"/>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B74" s="5">
         <v>74000</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R74" s="7"/>
       <c r="S74" s="7"/>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B75" s="5">
         <v>546539</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R75" s="7"/>
       <c r="S75" s="7"/>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B76" s="5">
         <v>1528857</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B77" s="5">
         <v>665634</v>
@@ -3611,39 +3611,39 @@
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B78" s="5">
         <v>1203000</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R78" s="7"/>
       <c r="S78" s="7"/>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B79" s="5">
         <v>333190</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R79" s="7"/>
       <c r="S79" s="7"/>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B80" s="5">
         <v>509212</v>
@@ -3667,7 +3667,7 @@
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B81" s="5">
         <v>716124</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B82" s="5">
         <v>250243</v>
@@ -3733,7 +3733,7 @@
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B83" s="11">
         <v>6843449</v>
@@ -3796,33 +3796,33 @@
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="R85" s="7"/>
       <c r="S85" s="7"/>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B86" s="5">
         <v>28078</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G86" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R86" s="7"/>
       <c r="S86" s="7"/>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B87" s="5">
         <v>28712</v>
@@ -3840,7 +3840,7 @@
         <v>3.1</v>
       </c>
       <c r="G87" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L87" s="7">
         <f t="shared" si="4"/>
@@ -3861,7 +3861,7 @@
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B88" s="5">
         <v>238689</v>
@@ -3879,7 +3879,7 @@
         <v>2.8</v>
       </c>
       <c r="G88" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L88" s="7">
         <f t="shared" si="4"/>
@@ -3900,7 +3900,7 @@
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B89" s="5">
         <v>75325</v>
@@ -3918,7 +3918,7 @@
         <v>2.4</v>
       </c>
       <c r="G89" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L89" s="7">
         <f t="shared" si="4"/>
@@ -3943,7 +3943,7 @@
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B91" s="5">
         <v>12200</v>
@@ -3980,7 +3980,7 @@
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B92" s="5">
         <v>74000</v>
@@ -3998,7 +3998,7 @@
         <v>2</v>
       </c>
       <c r="G92" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I92" s="5"/>
       <c r="L92" s="7">
@@ -4024,7 +4024,7 @@
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B94" s="11">
         <v>96052071</v>
@@ -4077,10 +4077,10 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C97" s="5">
         <v>2879</v>
@@ -4089,15 +4089,15 @@
         <v>2506</v>
       </c>
       <c r="G97" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C98" s="5">
         <v>1015</v>
@@ -4106,15 +4106,15 @@
         <v>725</v>
       </c>
       <c r="G98" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C99" s="5">
         <v>1172</v>
@@ -4123,15 +4123,15 @@
         <v>2069</v>
       </c>
       <c r="G99" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C101" s="5">
         <v>69484</v>
@@ -4140,24 +4140,24 @@
         <v>39620</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D102" s="5">
         <v>35671</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1884.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1884.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A51131-4A82-498E-BD50-D51DA1E0EB31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAED68C-31CD-49AF-B96B-F0CC5518E664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{E49FF23B-5D0B-4DAE-84F9-7D6D171212C5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="126">
   <si>
     <t>губ</t>
   </si>
@@ -333,9 +333,6 @@
     <t>Кронштадтское</t>
   </si>
   <si>
-    <t>Всего</t>
-  </si>
-  <si>
     <t>Итого области</t>
   </si>
   <si>
@@ -412,6 +409,12 @@
   </si>
   <si>
     <t>чу YY</t>
+  </si>
+  <si>
+    <t>Всего Империя</t>
+  </si>
+  <si>
+    <t>note</t>
   </si>
 </sst>
 </file>
@@ -438,7 +441,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -463,6 +466,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -476,7 +491,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -494,7 +509,6 @@
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -503,6 +517,8 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -842,27 +858,27 @@
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -872,42 +888,42 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -917,7 +933,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -927,7 +943,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E98A1D34-8D50-4752-AD94-484EE1B49B45}">
-  <dimension ref="A1:S102"/>
+  <dimension ref="A1:S107"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="30.578125" customWidth="1"/>
@@ -950,7 +966,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>3</v>
@@ -959,7 +975,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
@@ -1138,8 +1154,8 @@
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="14" t="s">
-        <v>113</v>
+      <c r="A7" s="13" t="s">
+        <v>112</v>
       </c>
       <c r="B7" s="5">
         <v>406365</v>
@@ -2111,7 +2127,7 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B34" s="5">
         <v>757111</v>
@@ -3371,64 +3387,64 @@
       </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="10" t="s">
+      <c r="A69" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B69" s="11">
+      <c r="B69" s="10">
         <v>88825618</v>
       </c>
-      <c r="C69" s="11">
+      <c r="C69" s="10">
         <v>4324216</v>
       </c>
-      <c r="D69" s="11">
+      <c r="D69" s="10">
         <v>2900558</v>
       </c>
-      <c r="E69" s="12">
+      <c r="E69" s="11">
         <v>4.88</v>
       </c>
-      <c r="F69" s="12">
+      <c r="F69" s="11">
         <v>3.26</v>
       </c>
-      <c r="G69" s="12"/>
-      <c r="H69" s="10"/>
-      <c r="I69" s="11">
+      <c r="G69" s="11"/>
+      <c r="H69" s="9"/>
+      <c r="I69" s="10">
         <f>SUM(B3:B68)-B51-B34-B7</f>
         <v>88798618</v>
       </c>
-      <c r="J69" s="11">
+      <c r="J69" s="10">
         <f>SUM(C3:C68)-C51-C34-C7</f>
         <v>4324216</v>
       </c>
-      <c r="K69" s="11">
+      <c r="K69" s="10">
         <f>SUM(D3:D68)-D51-D34-D7</f>
         <v>2900558</v>
       </c>
-      <c r="L69" s="13">
+      <c r="L69" s="12">
         <f t="shared" si="4"/>
         <v>4.8682081784108728</v>
       </c>
-      <c r="M69" s="13">
+      <c r="M69" s="12">
         <f t="shared" si="5"/>
         <v>3.2654520906344833</v>
       </c>
-      <c r="N69" s="10"/>
-      <c r="O69" s="11">
+      <c r="N69" s="9"/>
+      <c r="O69" s="10">
         <f>B69-I69</f>
         <v>27000</v>
       </c>
-      <c r="P69" s="11">
+      <c r="P69" s="10">
         <f>C69-J69</f>
         <v>0</v>
       </c>
-      <c r="Q69" s="11">
+      <c r="Q69" s="10">
         <f>D69-K69</f>
         <v>0</v>
       </c>
-      <c r="R69" s="13">
+      <c r="R69" s="12">
         <f t="shared" si="6"/>
         <v>-1.1791821589127061E-2</v>
       </c>
-      <c r="S69" s="13">
+      <c r="S69" s="12">
         <f t="shared" si="7"/>
         <v>5.4520906344834863E-3</v>
       </c>
@@ -3480,11 +3496,11 @@
       <c r="B72" s="5">
         <v>43965</v>
       </c>
-      <c r="C72" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D72" s="15" t="s">
-        <v>100</v>
+      <c r="C72" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="R72" s="7"/>
       <c r="S72" s="7"/>
@@ -3496,11 +3512,11 @@
       <c r="B73" s="5">
         <v>509633</v>
       </c>
-      <c r="C73" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D73" s="15" t="s">
-        <v>100</v>
+      <c r="C73" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D73" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="R73" s="7"/>
       <c r="S73" s="7"/>
@@ -3512,11 +3528,11 @@
       <c r="B74" s="5">
         <v>74000</v>
       </c>
-      <c r="C74" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D74" s="15" t="s">
-        <v>100</v>
+      <c r="C74" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D74" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="R74" s="7"/>
       <c r="S74" s="7"/>
@@ -3528,11 +3544,11 @@
       <c r="B75" s="5">
         <v>546539</v>
       </c>
-      <c r="C75" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D75" s="15" t="s">
-        <v>100</v>
+      <c r="C75" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D75" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="R75" s="7"/>
       <c r="S75" s="7"/>
@@ -3616,11 +3632,11 @@
       <c r="B78" s="5">
         <v>1203000</v>
       </c>
-      <c r="C78" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D78" s="15" t="s">
-        <v>100</v>
+      <c r="C78" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D78" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="R78" s="7"/>
       <c r="S78" s="7"/>
@@ -3632,11 +3648,11 @@
       <c r="B79" s="5">
         <v>333190</v>
       </c>
-      <c r="C79" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D79" s="15" t="s">
-        <v>100</v>
+      <c r="C79" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D79" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="R79" s="7"/>
       <c r="S79" s="7"/>
@@ -3732,57 +3748,57 @@
       </c>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="B83" s="11">
+      <c r="A83" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B83" s="10">
         <v>6843449</v>
       </c>
-      <c r="C83" s="11">
+      <c r="C83" s="10">
         <v>143777</v>
       </c>
-      <c r="D83" s="11">
+      <c r="D83" s="10">
         <v>90695</v>
       </c>
-      <c r="E83" s="13"/>
-      <c r="F83" s="13"/>
-      <c r="G83" s="13"/>
-      <c r="H83" s="10"/>
-      <c r="I83" s="11">
+      <c r="E83" s="12"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="12"/>
+      <c r="H83" s="9"/>
+      <c r="I83" s="10">
         <f>SUM(B71:B82)</f>
         <v>6843449</v>
       </c>
-      <c r="J83" s="11">
+      <c r="J83" s="10">
         <f>SUM(C71:C82)</f>
         <v>143777</v>
       </c>
-      <c r="K83" s="11">
+      <c r="K83" s="10">
         <f>SUM(D71:D82)</f>
         <v>90695</v>
       </c>
-      <c r="L83" s="13">
+      <c r="L83" s="12">
         <f t="shared" si="4"/>
         <v>2.1009435446950797</v>
       </c>
-      <c r="M83" s="13">
+      <c r="M83" s="12">
         <f t="shared" si="5"/>
         <v>1.3252820324956027</v>
       </c>
-      <c r="N83" s="10"/>
-      <c r="O83" s="11">
+      <c r="N83" s="9"/>
+      <c r="O83" s="10">
         <f>B83-I83</f>
         <v>0</v>
       </c>
-      <c r="P83" s="11">
+      <c r="P83" s="10">
         <f>C83-J83</f>
         <v>0</v>
       </c>
-      <c r="Q83" s="11">
+      <c r="Q83" s="10">
         <f>D83-K83</f>
         <v>0</v>
       </c>
-      <c r="R83" s="13"/>
-      <c r="S83" s="13"/>
+      <c r="R83" s="12"/>
+      <c r="S83" s="12"/>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="I84" s="5"/>
@@ -3795,8 +3811,8 @@
       <c r="S84" s="7"/>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="9" t="s">
-        <v>111</v>
+      <c r="A85" s="15" t="s">
+        <v>110</v>
       </c>
       <c r="R85" s="7"/>
       <c r="S85" s="7"/>
@@ -3808,11 +3824,11 @@
       <c r="B86" s="5">
         <v>28078</v>
       </c>
-      <c r="C86" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D86" s="15" t="s">
-        <v>100</v>
+      <c r="C86" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D86" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="G86" t="s">
         <v>67</v>
@@ -3948,34 +3964,26 @@
       <c r="B91" s="5">
         <v>12200</v>
       </c>
-      <c r="C91" s="5">
-        <v>320</v>
-      </c>
-      <c r="D91" s="5">
-        <v>319</v>
-      </c>
-      <c r="E91" s="8">
-        <v>2.62</v>
-      </c>
-      <c r="F91" s="8">
-        <v>2.61</v>
-      </c>
-      <c r="G91" s="8"/>
+      <c r="E91" s="8"/>
+      <c r="F91" s="8"/>
+      <c r="G91" t="s">
+        <v>88</v>
+      </c>
       <c r="L91" s="7">
         <f t="shared" si="4"/>
-        <v>2.622950819672131</v>
+        <v>0</v>
       </c>
       <c r="M91" s="7">
         <f t="shared" si="5"/>
-        <v>2.6147540983606556</v>
+        <v>0</v>
       </c>
       <c r="R91" s="7">
         <f t="shared" si="6"/>
-        <v>2.9508196721308444E-3</v>
+        <v>0</v>
       </c>
       <c r="S91" s="7">
         <f t="shared" si="7"/>
-        <v>4.7540983606557674E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.55000000000000004">
@@ -4023,64 +4031,64 @@
       <c r="S93" s="7"/>
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B94" s="11">
+      <c r="A94" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B94" s="10">
         <v>96052071</v>
       </c>
-      <c r="C94" s="11">
+      <c r="C94" s="10">
         <v>4482287</v>
       </c>
-      <c r="D94" s="11">
+      <c r="D94" s="10">
         <v>3001267</v>
       </c>
-      <c r="E94" s="13"/>
-      <c r="F94" s="13"/>
-      <c r="G94" s="13"/>
-      <c r="H94" s="10"/>
-      <c r="I94" s="11">
+      <c r="E94" s="12"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
+      <c r="H94" s="9"/>
+      <c r="I94" s="10">
         <f>I83+I69+SUM(B86:B92)-B92</f>
         <v>96025071</v>
       </c>
-      <c r="J94" s="11">
+      <c r="J94" s="10">
         <f>J83+J69+SUM(C86:C92)-C92</f>
-        <v>4482287</v>
-      </c>
-      <c r="K94" s="11">
+        <v>4481967</v>
+      </c>
+      <c r="K94" s="10">
         <f>K83+K69+SUM(D86:D92)-D92</f>
-        <v>3001267</v>
-      </c>
-      <c r="L94" s="13">
+        <v>3000948</v>
+      </c>
+      <c r="L94" s="12">
         <f t="shared" si="4"/>
         <v>4.6665178099075035</v>
       </c>
-      <c r="M94" s="13">
+      <c r="M94" s="12">
         <f t="shared" si="5"/>
         <v>3.1246249755510216</v>
       </c>
-      <c r="N94" s="10"/>
-      <c r="O94" s="11">
+      <c r="N94" s="9"/>
+      <c r="O94" s="10">
         <f>B94-I94</f>
         <v>27000</v>
       </c>
-      <c r="P94" s="11">
+      <c r="P94" s="10">
         <f>C94-J94</f>
-        <v>0</v>
-      </c>
-      <c r="Q94" s="11">
+        <v>320</v>
+      </c>
+      <c r="Q94" s="10">
         <f>D94-K94</f>
-        <v>0</v>
-      </c>
-      <c r="R94" s="13"/>
-      <c r="S94" s="13"/>
+        <v>319</v>
+      </c>
+      <c r="R94" s="12"/>
+      <c r="S94" s="12"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
-        <v>116</v>
-      </c>
-      <c r="B97" s="15" t="s">
-        <v>100</v>
+        <v>115</v>
+      </c>
+      <c r="B97" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="C97" s="5">
         <v>2879</v>
@@ -4094,10 +4102,10 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
-        <v>117</v>
-      </c>
-      <c r="B98" s="15" t="s">
-        <v>100</v>
+        <v>116</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="C98" s="5">
         <v>1015</v>
@@ -4111,10 +4119,10 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
-        <v>118</v>
-      </c>
-      <c r="B99" s="15" t="s">
-        <v>100</v>
+        <v>117</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="C99" s="5">
         <v>1172</v>
@@ -4128,10 +4136,10 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
-        <v>120</v>
-      </c>
-      <c r="B101" s="15" t="s">
-        <v>100</v>
+        <v>119</v>
+      </c>
+      <c r="B101" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="C101" s="5">
         <v>69484</v>
@@ -4140,24 +4148,49 @@
         <v>39620</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
-        <v>121</v>
-      </c>
-      <c r="B102" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="C102" s="15" t="s">
-        <v>100</v>
+        <v>120</v>
+      </c>
+      <c r="B102" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C102" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="D102" s="5">
         <v>35671</v>
       </c>
       <c r="G102" s="7" t="s">
         <v>71</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A105" s="16" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" t="s">
+        <v>96</v>
+      </c>
+      <c r="B107" s="5">
+        <v>12200</v>
+      </c>
+      <c r="C107" s="5">
+        <v>320</v>
+      </c>
+      <c r="D107" s="5">
+        <v>319</v>
+      </c>
+      <c r="E107" s="8">
+        <v>2.62</v>
+      </c>
+      <c r="F107" s="8">
+        <v>2.61</v>
       </c>
     </row>
   </sheetData>

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1884.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1884.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAED68C-31CD-49AF-B96B-F0CC5518E664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F50556-4982-4E79-90C0-CA209C1EE74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{E49FF23B-5D0B-4DAE-84F9-7D6D171212C5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="127">
   <si>
     <t>губ</t>
   </si>
@@ -415,6 +415,9 @@
   </si>
   <si>
     <t>note</t>
+  </si>
+  <si>
+    <t>Ферганская (одни русские)</t>
   </si>
 </sst>
 </file>
@@ -943,7 +946,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E98A1D34-8D50-4752-AD94-484EE1B49B45}">
-  <dimension ref="A1:S107"/>
+  <dimension ref="A1:S108"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="30.578125" customWidth="1"/>
@@ -3688,28 +3691,14 @@
       <c r="B81" s="5">
         <v>716124</v>
       </c>
-      <c r="C81" s="5">
-        <v>223</v>
-      </c>
-      <c r="D81" s="5">
-        <v>137</v>
-      </c>
-      <c r="L81" s="7">
-        <f t="shared" si="4"/>
-        <v>3.1139858460266658E-2</v>
-      </c>
-      <c r="M81" s="7">
-        <f t="shared" si="5"/>
-        <v>1.9130765063033777E-2</v>
-      </c>
-      <c r="R81" s="7">
-        <f t="shared" si="6"/>
-        <v>3.1139858460266658E-2</v>
-      </c>
-      <c r="S81" s="7">
-        <f t="shared" si="7"/>
-        <v>1.9130765063033777E-2</v>
-      </c>
+      <c r="C81" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D81" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="R81" s="7"/>
+      <c r="S81" s="7"/>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
@@ -3770,11 +3759,11 @@
       </c>
       <c r="J83" s="10">
         <f>SUM(C71:C82)</f>
-        <v>143777</v>
+        <v>143554</v>
       </c>
       <c r="K83" s="10">
         <f>SUM(D71:D82)</f>
-        <v>90695</v>
+        <v>90558</v>
       </c>
       <c r="L83" s="12">
         <f t="shared" si="4"/>
@@ -3791,11 +3780,11 @@
       </c>
       <c r="P83" s="10">
         <f>C83-J83</f>
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="Q83" s="10">
         <f>D83-K83</f>
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="R83" s="12"/>
       <c r="S83" s="12"/>
@@ -4053,11 +4042,11 @@
       </c>
       <c r="J94" s="10">
         <f>J83+J69+SUM(C86:C92)-C92</f>
-        <v>4481967</v>
+        <v>4481744</v>
       </c>
       <c r="K94" s="10">
         <f>K83+K69+SUM(D86:D92)-D92</f>
-        <v>3000948</v>
+        <v>3000811</v>
       </c>
       <c r="L94" s="12">
         <f t="shared" si="4"/>
@@ -4074,11 +4063,11 @@
       </c>
       <c r="P94" s="10">
         <f>C94-J94</f>
-        <v>320</v>
+        <v>543</v>
       </c>
       <c r="Q94" s="10">
         <f>D94-K94</f>
-        <v>319</v>
+        <v>456</v>
       </c>
       <c r="R94" s="12"/>
       <c r="S94" s="12"/>
@@ -4191,6 +4180,17 @@
       </c>
       <c r="F107" s="8">
         <v>2.61</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" t="s">
+        <v>126</v>
+      </c>
+      <c r="C108" s="5">
+        <v>223</v>
+      </c>
+      <c r="D108" s="5">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
